--- a/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles. Papa dit : il a besoin d'eau. Il a besoin de lumière. Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic. Papa dit : on arrose avec un adulte.</t>
+          <t>Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles. Il a besoin d'eau. Il a besoin de lumière. Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic. On arrose avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles.
+papa|Il a besoin d'eau. Il a besoin de lumière.
+narrateur|Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic.
+papa|On arrose avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le basilic a soif. Que fait Mateo avec papa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Mateo a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Mateo range l'arrosoir. Le basilic tient droit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|On arrose avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Le basilic a soif. Que fait Mateo avec papa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Mateo a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Mateo range l'arrosoir. Le basilic tient droit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mateo arrose le basilic</t>
+          <t>La terre comme du sable</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut sentir une feuille de basilic. La terre est sèche comme du sable. L'eau glisse sur le côté. Une goutte, puis encore. La terre s'assombrit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles. Il a besoin d'eau. Il a besoin de lumière. Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic. On arrose avec un adulte.</t>
+          <t>Un rayon jaune coupe la table. Des miettes brillent dedans. Le basilic est sur le rebord. Ça sent le bois chaud. Une chaise racle un peu le sol. Raphaël vit ici, avec papa. Tu as vu la terre ? Elle est claire. Papa pince un peu de terre. Elle tombe, comme du sable. Du sable ? Elle a trop soif. Tu veux sentir une feuille ? Oui. Mais elle est molle. On lui donne de l'eau. Tu prends l'arrosoir ? En ce moment, Raphaël tire l'anse. L'arrosoir est petit, rouge. L'eau cloche, pas trop. Je verse ? Une goutte d'abord. Puis encore. Raphaël penche. L'eau glisse sur le côté. Elle tombe sur le bois. Elle ne rentre pas ! La terre est trop sèche. Elle fait un toit. Une miette brille encore. Raphaël la pousse du doigt. On recommence ? Oui. Au milieu, cette fois. Le petit arrosoir rouge tremble. Raphaël le tient à deux mains. J'ai peur de trop verser. Une goutte seulement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles. Papa dit : il a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Il a besoin de lumière. Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic. Papa dit : on arrose avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un rayon jaune coupe la table. Des miettes brillent dedans. Le basilic est sur le rebord. Ça sent le bois chaud. Une chaise racle un peu le sol. Raphaël vit ici, avec papa. Tu as vu la terre ? Elle est claire. Papa pince un peu de terre. Elle tombe, comme du sable. Du sable ? Elle a trop soif. Tu veux sentir une feuille ? Oui. Mais elle est molle. On lui donne de l'eau. Tu prends l'arrosoir ? En ce moment, Raphaël tire l'anse. L'arrosoir est petit, rouge. L'eau cloche, pas trop. Je verse ? Une goutte d'abord. Puis encore. Raphaël penche. L'eau glisse sur le côté. Elle tombe sur le bois. Elle ne rentre pas ! La terre est trop sèche. Elle fait un toit. Une miette brille encore. Raphaël la pousse du doigt. On recommence ? Oui. Au milieu, cette fois. Le petit arrosoir rouge tremble. Raphaël le tient à deux mains. J'ai peur de trop verser. Une goutte seulement.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,46 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Mateo est près de la fenêtre. Papa est là. Un petit basilic a soif. Ses feuilles sont molles.
-papa|Il a besoin d'eau. Il a besoin de lumière.
-narrateur|Mateo prend l'arrosoir avec papa. Ils versent un peu d'eau. La terre devient sombre. Papa pose le pot près de la fenêtre. La lumière arrive. Mateo touche une feuille. Ça sent le basilic.
-papa|On arrose avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un rayon jaune coupe la table.
+narrateur|Des miettes brillent dedans.
+narrateur|Le basilic est sur le rebord.
+narrateur|Ça sent le bois chaud.
+narrateur|Une chaise racle un peu le sol.
+narrateur|Raphaël vit ici, avec papa.
+papa|Tu as vu la terre ?
+enfant-m|Elle est claire.
+narrateur|Papa pince un peu de terre.
+narrateur|Elle tombe, comme du sable.
+enfant-m|Du sable ?
+papa|Elle a trop soif.
+papa|Tu veux sentir une feuille ?
+enfant-m|Oui.
+enfant-m|Mais elle est molle.
+papa|On lui donne de l'eau.
+papa|Tu prends l'arrosoir ?
+narrateur|En ce moment, Raphaël tire l'anse.
+narrateur|L'arrosoir est petit, rouge.
+narrateur|L'eau cloche, pas trop.
+enfant-m|Je verse ?
+papa|Une goutte d'abord.
+papa|Puis encore.
+narrateur|Raphaël penche.
+narrateur|L'eau glisse sur le côté.
+narrateur|Elle tombe sur le bois.
+enfant-m|Elle ne rentre pas !
+papa|La terre est trop sèche.
+papa|Elle fait un toit.
+narrateur|Une miette brille encore.
+narrateur|Raphaël la pousse du doigt.
+enfant-m|On recommence ?
+papa|Oui.
+papa|Au milieu, cette fois.
+narrateur|Le petit arrosoir rouge tremble.
+narrateur|Raphaël le tient à deux mains.
+enfant-m|J'ai peur de trop verser.
+papa|Une goutte seulement.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1388,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le basilic a soif. Que fait Mateo avec papa ?</t>
+          <t>Le basilic a soif. Que fait Raphaël avec papa ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le basilic a soif. Que fait Mateo avec papa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le basilic a soif. Que fait Raphaël avec papa ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1378,7 +1423,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Mateo ?</t>
+          <t>Ils versent de l'eau. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1472,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1544,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le basilic a soif. Que fait Mateo avec papa ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le basilic a soif.
+narrateur|Que fait Raphaël avec papa ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1572,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Mateo a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+          <t>Papa pose un doigt au milieu. Ici. Une goutte, au centre. Raphaël verse une goutte. La goutte reste, un instant. Puis elle s'enfonce. Elle est partie. Encore une. Encore une goutte. Puis encore. Un rond sombre s'ouvre. Elle boit, là. Oui. Tout doux. La terre n'est plus du sable. Elle devient sombre, au milieu. Merci, Raphaël. Tu as versé goutte à goutte. Je peux sentir ? Bientôt. On attend un peu. Ils regardent le rond sombre. Il s'élargit, tout lentement. Il grandit. La terre boit, au fond. Une feuille bouge, à peine. Le rayon jaune la touche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mateo a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Papa, l'adulte, était avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose un doigt au milieu. Ici. Une goutte, au centre. Raphaël verse une goutte. La goutte reste, un instant. Puis elle s'enfonce. Elle est partie. Encore une. Encore une goutte. Puis encore. Un rond sombre s'ouvre. Elle boit, là. Oui. Tout doux. La terre n'est plus du sable. Elle devient sombre, au milieu. Merci, Raphaël. Tu as versé goutte à goutte. Je peux sentir ? Bientôt. On attend un peu. Ils regardent le rond sombre. Il s'élargit, tout lentement. Il grandit. La terre boit, au fond. Une feuille bouge, à peine. Le rayon jaune la touche.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1588,14 +1633,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1716,35 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Mateo a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Papa pose un doigt au milieu.
+papa|Ici.
+papa|Une goutte, au centre.
+narrateur|Raphaël verse une goutte.
+narrateur|La goutte reste, un instant.
+narrateur|Puis elle s'enfonce.
+enfant-m|Elle est partie.
+papa|Encore une.
+narrateur|Encore une goutte.
+narrateur|Puis encore.
+narrateur|Un rond sombre s'ouvre.
+enfant-m|Elle boit, là.
+papa|Oui.
+papa|Tout doux.
+narrateur|La terre n'est plus du sable.
+narrateur|Elle devient sombre, au milieu.
+papa|Merci, Raphaël.
+papa|Tu as versé goutte à goutte.
+enfant-m|Je peux sentir ?
+papa|Bientôt.
+papa|On attend un peu.
+narrateur|Ils regardent le rond sombre.
+narrateur|Il s'élargit, tout lentement.
+enfant-m|Il grandit.
+papa|La terre boit, au fond.
+narrateur|Une feuille bouge, à peine.
+narrateur|Le rayon jaune la touche.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mateo range l'arrosoir. Le basilic tient droit.</t>
+          <t>Ils attendent près du rebord. Le rayon jaune a bougé. La feuille ? Touche, tout doux. Raphaël touche. La feuille est moins molle. Elle se lève. Un peu, oui. Raphaël approche le nez. L'odeur est encore faible. Presque. Froisse tout doux. Raphaël froisse. L'odeur arrive, verte, nette. Ça y est ! Oui. Une goutte, puis encore. Une dernière goutte brille. Puis elle s'enfonce. Tu as fini de sentir ? Encore. Raphaël froisse une deuxième fois. L'odeur est plus forte. Maintenant, oui. Bien. Raphaël essuie une goutte sur le bois. Le bois redevient sec. Tu as fini le rebord ? Oui, papa. Merci.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Mateo range l'arrosoir. Le basilic tient droit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils attendent près du rebord. Le rayon jaune a bougé. La feuille ? Touche, tout doux. Raphaël touche. La feuille est moins molle. Elle se lève. Un peu, oui. Raphaël approche le nez. L'odeur est encore faible. Presque. Froisse tout doux. Raphaël froisse. L'odeur arrive, verte, nette. Ça y est ! Oui. Une goutte, puis encore. Une dernière goutte brille. Puis elle s'enfonce. Tu as fini de sentir ? Encore. Raphaël froisse une deuxième fois. L'odeur est plus forte. Maintenant, oui. Bien. Raphaël essuie une goutte sur le bois. Le bois redevient sec. Tu as fini le rebord ? Oui, papa. Merci.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1760,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1905,38 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mateo range l'arrosoir. Le basilic tient droit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils attendent près du rebord.
+narrateur|Le rayon jaune a bougé.
+enfant-m|La feuille ?
+papa|Touche, tout doux.
+narrateur|Raphaël touche.
+narrateur|La feuille est moins molle.
+enfant-m|Elle se lève.
+papa|Un peu, oui.
+narrateur|Raphaël approche le nez.
+narrateur|L'odeur est encore faible.
+enfant-m|Presque.
+papa|Froisse tout doux.
+narrateur|Raphaël froisse.
+narrateur|L'odeur arrive, verte, nette.
+enfant-m|Ça y est !
+papa|Oui.
+papa|Une goutte, puis encore.
+narrateur|Une dernière goutte brille.
+narrateur|Puis elle s'enfonce.
+papa|Tu as fini de sentir ?
+enfant-m|Encore.
+narrateur|Raphaël froisse une deuxième fois.
+narrateur|L'odeur est plus forte.
+enfant-m|Maintenant, oui.
+papa|Bien.
+narrateur|Raphaël essuie une goutte sur le bois.
+narrateur|Le bois redevient sec.
+papa|Tu as fini le rebord ?
+enfant-m|Oui, papa.
+papa|Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël garde le vert aux doigts. J'ai senti. Oui. La terre n'est plus du sable. Une dernière goutte brille sur la terre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël garde le vert aux doigts. J'ai senti. Oui. La terre n'est plus du sable. Une dernière goutte brille sur la terre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +2022,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2101,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Raphaël garde le vert aux doigts.
+enfant-m|J'ai senti.
+papa|Oui.
+papa|La terre n'est plus du sable.
+narrateur|Une dernière goutte brille sur la terre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mateo, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
